--- a/downloads/exportExcelInternalJObFilter2.xlsx
+++ b/downloads/exportExcelInternalJObFilter2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Job ID</t>
   </si>
@@ -85,45 +85,12 @@
     <t>In progressDX</t>
   </si>
   <si>
-    <t>J-695</t>
+    <t>J-706</t>
   </si>
   <si>
     <t>Installation5</t>
   </si>
   <si>
-    <t>Anil Rathor</t>
-  </si>
-  <si>
-    <t>9103456789</t>
-  </si>
-  <si>
-    <t>Gujarat</t>
-  </si>
-  <si>
-    <t>Jamnagar</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>28/02/2026</t>
-  </si>
-  <si>
-    <t>J-694</t>
-  </si>
-  <si>
-    <t>9863574112</t>
-  </si>
-  <si>
-    <t>J-693</t>
-  </si>
-  <si>
-    <t>J-692</t>
-  </si>
-  <si>
-    <t>J-664</t>
-  </si>
-  <si>
     <t>Mayank Rathor</t>
   </si>
   <si>
@@ -136,7 +103,7 @@
     <t>createdD</t>
   </si>
   <si>
-    <t>21/02/2026</t>
+    <t>02/03/2026</t>
   </si>
 </sst>
 </file>
@@ -513,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -623,177 +590,25 @@
         <v>27</v>
       </c>
       <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
         <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
